--- a/144/DQ Templates and Instructions/Topic 1 DQ 2/Topic 1 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 1 DQ 2/Topic 1 DQ 2.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 1 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="8_{F0DFF4ED-F49F-4D0C-BB64-AFBFCD3897EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872B22C2-340C-4A36-A8BA-3E99E145BC92}"/>
+  <xr:revisionPtr revIDLastSave="609" documentId="8_{F0DFF4ED-F49F-4D0C-BB64-AFBFCD3897EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{957A749B-E279-474D-8B50-7A61CEDCF0B4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA857894-CCDD-4590-8F7E-A65A6A8D0808}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="4" r:id="rId1"/>
     <sheet name="Linear Fit" sheetId="1" r:id="rId2"/>
-    <sheet name="GradeSheet" sheetId="5" state="hidden" r:id="rId3"/>
-    <sheet name="Random" sheetId="2" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="Users" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="GradeSheet" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Random" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="rangepred">_xlfn.LAMBDA(_xlpm.x,AND(_xlpm.x &lt;&gt; "", IFERROR(OR(SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT(_xlpm.x), " ",""),"$","") = "=E17:E27*B26+B25",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT(_xlpm.x), " ",""),"$","") = "=B25+E17:E27*B26",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT(_xlpm.x), " ",""),"$","") = "=B25+B26*E17:E27",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT(_xlpm.x), " ",""),"$","") = "=B26*E17:E27+B25"), FALSE)))</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <customWorkbookViews>
     <customWorkbookView name="Richard Ketchersid - Personal View" guid="{1E6EB3EC-58F4-42D5-9462-6EAD6EC3491E}" mergeInterval="0" personalView="1" xWindow="61" yWindow="61" windowWidth="1733" windowHeight="952" activeSheetId="1" showComments="commIndAndComment"/>
   </customWorkbookViews>
@@ -113,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -427,12 +428,18 @@
   <si>
     <t>Video for this DQ</t>
   </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,18 +534,6 @@
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Baguet Script"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -958,7 +953,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -987,7 +982,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
@@ -1039,7 +1034,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1141,6 +1136,13 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1348,19 +1350,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1416,19 +1418,19 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
@@ -2285,58 +2287,58 @@
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
     </row>
     <row r="4" spans="2:9" ht="30">
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
     </row>
     <row r="6" spans="2:9" ht="30">
       <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="2:9" ht="30.75" thickBot="1">
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="68"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" thickBot="1">
       <c r="B8" s="7"/>
@@ -2397,36 +2399,36 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" thickBot="1"/>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="118"/>
-      <c r="I2" s="106" t="s">
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="120"/>
+      <c r="I2" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="108"/>
-      <c r="O2" s="72" t="s">
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="110"/>
+      <c r="O2" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="73"/>
+      <c r="P2" s="75"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1">
-      <c r="C3" s="119"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="121"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="111"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="123"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="113"/>
       <c r="O3" s="35" t="s">
         <v>13</v>
       </c>
@@ -2443,20 +2445,20 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="14.45" customHeight="1">
-      <c r="C5" s="106" t="s">
+      <c r="C5" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="108"/>
-      <c r="I5" s="106" t="s">
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="110"/>
+      <c r="I5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="108"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="110"/>
       <c r="O5" s="39" t="s">
         <v>18</v>
       </c>
@@ -2465,16 +2467,16 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="111"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="113"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="112"/>
+      <c r="M6" s="113"/>
       <c r="O6" s="40" t="s">
         <v>20</v>
       </c>
@@ -2491,12 +2493,12 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1">
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="124"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
       <c r="F8" s="55" t="s">
         <v>12</v>
       </c>
@@ -2510,123 +2512,123 @@
         <f>IF(LEN(F8)&lt;5,"Too Short","")</f>
         <v/>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="88"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="90"/>
       <c r="O9" s="43">
         <v>15</v>
       </c>
-      <c r="P9" s="95" t="s">
+      <c r="P9" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="95"/>
-      <c r="S9" s="96"/>
+      <c r="Q9" s="97"/>
+      <c r="R9" s="97"/>
+      <c r="S9" s="98"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="88"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="91"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="93"/>
       <c r="O10" s="44">
         <v>15</v>
       </c>
-      <c r="P10" s="97" t="s">
+      <c r="P10" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="97"/>
-      <c r="S10" s="98"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="100"/>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A11" s="45"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="91"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="94"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="93"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="96"/>
       <c r="O11" s="46">
         <v>16</v>
       </c>
-      <c r="P11" s="99" t="s">
+      <c r="P11" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="100"/>
+      <c r="Q11" s="101"/>
+      <c r="R11" s="101"/>
+      <c r="S11" s="102"/>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A12" s="47"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="91"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="93"/>
       <c r="O12" s="48">
         <v>16</v>
       </c>
-      <c r="P12" s="101" t="s">
+      <c r="P12" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="102"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="104"/>
     </row>
     <row r="13" spans="1:19" ht="18" customHeight="1" thickBot="1">
       <c r="A13" s="45"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="94"/>
-      <c r="I13" s="74" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="96"/>
+      <c r="I13" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="76"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="78"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1">
       <c r="A14" s="45"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="81"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="B15" s="133" t="s">
+      <c r="B15" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="134"/>
+      <c r="C15" s="136"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="133" t="s">
+      <c r="E15" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="134"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="79"/>
+      <c r="F15" s="136"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="81"/>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="50" t="s">
@@ -2641,11 +2643,11 @@
       <c r="F16" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="77"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="81"/>
     </row>
     <row r="17" spans="2:14">
       <c r="B17" s="4" t="str">
@@ -2661,11 +2663,11 @@
         <v>Check F8</v>
       </c>
       <c r="F17" s="30"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="81"/>
     </row>
     <row r="18" spans="2:14">
       <c r="B18" s="2" t="str">
@@ -2681,11 +2683,11 @@
         <v>Check F8</v>
       </c>
       <c r="F18" s="30"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="81"/>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" s="2" t="str">
@@ -2701,11 +2703,11 @@
         <v>Check F8</v>
       </c>
       <c r="F19" s="30"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="81"/>
     </row>
     <row r="20" spans="2:14">
       <c r="B20" s="2" t="str">
@@ -2721,11 +2723,11 @@
         <v>Check F8</v>
       </c>
       <c r="F20" s="30"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="81"/>
     </row>
     <row r="21" spans="2:14">
       <c r="B21" s="2" t="str">
@@ -2741,11 +2743,11 @@
         <v>Check F8</v>
       </c>
       <c r="F21" s="30"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="81"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1">
       <c r="B22" s="3" t="str">
@@ -2761,11 +2763,11 @@
         <v>Check F8</v>
       </c>
       <c r="F22" s="30"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="79"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="81"/>
     </row>
     <row r="23" spans="2:14" ht="15.75" thickBot="1">
       <c r="E23" s="2" t="str">
@@ -2773,27 +2775,27 @@
         <v>Check F8</v>
       </c>
       <c r="F23" s="30"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="81"/>
     </row>
     <row r="24" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="136"/>
+      <c r="C24" s="138"/>
       <c r="E24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Check F8</v>
       </c>
       <c r="F24" s="30"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="84"/>
     </row>
     <row r="25" spans="2:14" ht="15.75" thickBot="1">
       <c r="B25" s="10"/>
@@ -2816,22 +2818,22 @@
         <v>Check F8</v>
       </c>
       <c r="F26" s="30"/>
-      <c r="H26" s="83" t="str">
+      <c r="H26" s="85" t="str">
         <f>IF(E9,"Check F3","Use your graph to approximate the stopping distance at a speed of  "&amp;(E25+E26)/2&amp;" m/s")</f>
         <v>Check F3</v>
       </c>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="87"/>
       <c r="N26" s="32"/>
     </row>
     <row r="27" spans="2:14" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B27" s="129" t="s">
+      <c r="B27" s="131" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="130"/>
+      <c r="C27" s="132"/>
       <c r="E27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Check F8</v>
@@ -2839,67 +2841,67 @@
       <c r="F27" s="30"/>
     </row>
     <row r="28" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B28" s="131"/>
-      <c r="C28" s="132"/>
-      <c r="E28" s="129" t="s">
+      <c r="B28" s="133"/>
+      <c r="C28" s="134"/>
+      <c r="E28" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="130"/>
-      <c r="H28" s="103" t="s">
+      <c r="F28" s="132"/>
+      <c r="H28" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="105"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="106"/>
+      <c r="N28" s="107"/>
     </row>
     <row r="29" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-      <c r="H29" s="69" t="s">
+      <c r="E29" s="133"/>
+      <c r="F29" s="134"/>
+      <c r="H29" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
       <c r="K29" s="33"/>
-      <c r="L29" s="67" t="s">
+      <c r="L29" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="M29" s="67"/>
-      <c r="N29" s="68"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="70"/>
     </row>
     <row r="30" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B30" s="125" t="s">
+      <c r="B30" s="127" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="126"/>
-      <c r="H30" s="69" t="s">
+      <c r="C30" s="128"/>
+      <c r="H30" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="71"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="73"/>
       <c r="M30" s="33"/>
       <c r="N30" s="54" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B31" s="127"/>
-      <c r="C31" s="128"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="130"/>
     </row>
     <row r="32" spans="2:14" ht="14.45" customHeight="1">
-      <c r="B32" s="112" t="s">
+      <c r="B32" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="113"/>
+      <c r="C32" s="115"/>
     </row>
     <row r="33" spans="2:3" ht="15.75" thickBot="1">
-      <c r="B33" s="114"/>
-      <c r="C33" s="115"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="117"/>
     </row>
     <row r="68" spans="5:5">
       <c r="E68" s="34" t="s">
@@ -2996,6 +2998,169 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40BB9AA7-BB63-4166-8E6B-03E152B02ECD}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="58"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="59">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>'Linear Fit'!F8</f>
+        <v>Your Name</v>
+      </c>
+      <c r="F1" s="58" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="58" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="58" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="58" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="58" t="str">
+        <f ca="1">IF(C$1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="U0MyB3qEd0GVCb85iAGicDJBi7FiWyaHGhMLLRl+j4eoN+vKu+bScvQ+U8Vs+ROGEJ/rXv6bvqoT3fZrXeHKEw==" saltValue="g+y06w8/Lxv/8rEFSgHH+A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC72E341-A7C9-447F-A0CE-0F63AD8EEA86}">
   <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3010,48 +3175,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
     </row>
     <row r="3" spans="1:15" ht="17.25" thickBot="1">
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="148"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="150"/>
       <c r="F3" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1"/>
     <row r="5" spans="1:15" ht="14.45" customHeight="1">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="151"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="153"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="B6" s="152"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="154"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="155"/>
+      <c r="D6" s="155"/>
+      <c r="E6" s="155"/>
+      <c r="F6" s="156"/>
       <c r="I6" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=E17:E27*B26+B25"</f>
         <v>#N/A</v>
@@ -3062,22 +3227,22 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="B7" s="152"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="154"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="156"/>
       <c r="I7" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+E17:E27*B26"</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B8" s="155"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="157"/>
+      <c r="B8" s="157"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="159"/>
       <c r="I8" s="13" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+B26*E17:E27"</f>
         <v>#N/A</v>
@@ -3093,15 +3258,15 @@
       <c r="O9" s="15"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="B10" s="158" t="s">
+      <c r="B10" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="159"/>
+      <c r="C10" s="161"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="158" t="s">
+      <c r="E10" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="159"/>
+      <c r="F10" s="161"/>
       <c r="I10" s="13" t="e">
         <f ca="1">OR(SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=E17:E27*B26+B25",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+E17:E27*B26",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B25+B26*E17:E27",SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Linear Fit'!F17), " ",""),"$","") = "=B26*E17:E27+B25")</f>
         <v>#N/A</v>
@@ -3384,10 +3549,10 @@
       </c>
     </row>
     <row r="19" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B19" s="137" t="s">
+      <c r="B19" s="139" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="138"/>
+      <c r="C19" s="140"/>
       <c r="E19" s="23" t="str">
         <f>'Linear Fit'!E24</f>
         <v>Check F8</v>
@@ -3524,14 +3689,14 @@
       </c>
     </row>
     <row r="23" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B23" s="137" t="s">
+      <c r="B23" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="138"/>
-      <c r="E23" s="139" t="s">
+      <c r="C23" s="140"/>
+      <c r="E23" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="140"/>
+      <c r="F23" s="142"/>
       <c r="H23" s="13" t="b">
         <f ca="1">AND(H12:H22)</f>
         <v>0</v>
@@ -3542,10 +3707,10 @@
       </c>
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B24" s="143"/>
-      <c r="C24" s="144"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="142"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="146"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="144"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NP8KfZBdrRoMbO4+6K5mYP0YLFWU9vooHr25DXKnzf2iWNfCPBeST5gJcYchWDz1uCvu2t4wrx5R4CXYPCjDLw==" saltValue="iJTkW+8OkP+1lMG5ccDKfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -3568,7 +3733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA233362-47A8-4EAC-A04C-EF1DCF03C8B4}">
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5142,60 +5307,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6006A5B-4015-4513-BD86-66A981B08642}">
   <dimension ref="C5:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="3:8">
-      <c r="C5" s="160" t="s">
+      <c r="C5" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="162"/>
     </row>
     <row r="6" spans="3:8">
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="160"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="160"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="162"/>
+      <c r="E8" s="162"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="162"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="160"/>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5207,6 +5372,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
@@ -5216,7 +5390,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5433,16 +5607,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8613C9D7-E17F-4BAF-838C-91D0DFFDABBA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4AD473-4FA9-46C1-A1D3-2EA805B81A69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5452,7 +5625,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8523C5DA-AB7D-4731-9E8F-F5765EA06D26}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5469,12 +5642,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8613C9D7-E17F-4BAF-838C-91D0DFFDABBA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>